--- a/data/raw/Rolled Treatments/rolled_combined_all.xlsx
+++ b/data/raw/Rolled Treatments/rolled_combined_all.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ey239/Github/Mowtivation/raw-data/Rolled Treatments/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ey239/Github/Mowtivation/data/raw/Rolled Treatments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23CAA52E-BC88-0347-85E8-DFA370D35708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E09CB4-7F32-1944-9B5C-F2714DDDE009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2320" yWindow="-20800" windowWidth="27640" windowHeight="16940" xr2:uid="{8F261457-9A0C-8A42-9440-1BA45DD83A86}"/>
+    <workbookView xWindow="19200" yWindow="-21000" windowWidth="19180" windowHeight="21000" xr2:uid="{8F261457-9A0C-8A42-9440-1BA45DD83A86}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="60">
   <si>
     <t>id</t>
   </si>
@@ -80,54 +80,15 @@
     <t>bean_yield</t>
   </si>
   <si>
-    <t>CU_B1_P103</t>
-  </si>
-  <si>
-    <t>field x</t>
-  </si>
-  <si>
     <t>RIM</t>
   </si>
   <si>
-    <t>CU_B1_P104</t>
-  </si>
-  <si>
     <t>RNO</t>
   </si>
   <si>
-    <t>CU_B1_P105</t>
-  </si>
-  <si>
     <t>RIC</t>
   </si>
   <si>
-    <t>CU_B1_P201</t>
-  </si>
-  <si>
-    <t>CU_B1_P202</t>
-  </si>
-  <si>
-    <t>CU_B1_P203</t>
-  </si>
-  <si>
-    <t>CU_B1_P303</t>
-  </si>
-  <si>
-    <t>CU_B1_P304</t>
-  </si>
-  <si>
-    <t>CU_B1_P305</t>
-  </si>
-  <si>
-    <t>CU_B1_P401</t>
-  </si>
-  <si>
-    <t>CU_B1_P402</t>
-  </si>
-  <si>
-    <t>CU_B1_P403</t>
-  </si>
-  <si>
     <t>field O2 west</t>
   </si>
   <si>
@@ -144,13 +105,124 @@
   </si>
   <si>
     <t>intrarow_mulch_biomass</t>
+  </si>
+  <si>
+    <t>V_2023_B1_P103</t>
+  </si>
+  <si>
+    <t>V_2023_B1_P104</t>
+  </si>
+  <si>
+    <t>V_2023_B1_P105</t>
+  </si>
+  <si>
+    <t>V_2023_B2_P201</t>
+  </si>
+  <si>
+    <t>V_2023_B2_P202</t>
+  </si>
+  <si>
+    <t>V_2023_B2_P203</t>
+  </si>
+  <si>
+    <t>V_2023_B3_P303</t>
+  </si>
+  <si>
+    <t>V_2023_B3_P304</t>
+  </si>
+  <si>
+    <t>V_2023_B3_P305</t>
+  </si>
+  <si>
+    <t>V_2023_B4_P401</t>
+  </si>
+  <si>
+    <t>V_2023_B4_P402</t>
+  </si>
+  <si>
+    <t>V_2023_B4_P403</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>O2W_2024_B1_P103</t>
+  </si>
+  <si>
+    <t>O2W_2024_B1_P104</t>
+  </si>
+  <si>
+    <t>O2W_2024_B1_P105</t>
+  </si>
+  <si>
+    <t>O2W_2024_B2_P201</t>
+  </si>
+  <si>
+    <t>O2W_2024_B2_P202</t>
+  </si>
+  <si>
+    <t>O2W_2024_B2_P203</t>
+  </si>
+  <si>
+    <t>O2W_2024_B3_P303</t>
+  </si>
+  <si>
+    <t>O2W_2024_B3_P304</t>
+  </si>
+  <si>
+    <t>O2W_2024_B3_P305</t>
+  </si>
+  <si>
+    <t>O2W_2024_B4_P401</t>
+  </si>
+  <si>
+    <t>O2W_2024_B4_P402</t>
+  </si>
+  <si>
+    <t>O2W_2024_B4_P403</t>
+  </si>
+  <si>
+    <t>O2E_2024_B1_P103</t>
+  </si>
+  <si>
+    <t>O2E_2024_B1_P104</t>
+  </si>
+  <si>
+    <t>O2E_2024_B1_P105</t>
+  </si>
+  <si>
+    <t>O2E_2024_B2_P201</t>
+  </si>
+  <si>
+    <t>O2E_2024_B2_P202</t>
+  </si>
+  <si>
+    <t>O2E_2024_B2_P203</t>
+  </si>
+  <si>
+    <t>O2E_2024_B3_P303</t>
+  </si>
+  <si>
+    <t>O2E_2024_B3_P304</t>
+  </si>
+  <si>
+    <t>O2E_2024_B3_P305</t>
+  </si>
+  <si>
+    <t>O2E_2024_B4_P401</t>
+  </si>
+  <si>
+    <t>O2E_2024_B4_P402</t>
+  </si>
+  <si>
+    <t>O2E_2024_B4_P403</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -161,6 +233,12 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -216,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -230,6 +308,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -567,7 +648,7 @@
   <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.1640625" customWidth="1"/>
     <col min="2" max="2" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -617,16 +698,16 @@
         <v>10</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>11</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="P1" s="5" t="s">
         <v>12</v>
@@ -635,18 +716,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>15</v>
+    <row r="2" spans="1:17" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="C2" s="6">
         <v>2023</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E2" s="6">
         <v>1</v>
@@ -670,16 +751,16 @@
         <v>3.92</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="M2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="N2">
         <v>285.95</v>
       </c>
       <c r="O2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="P2">
         <v>37.5</v>
@@ -688,18 +769,18 @@
         <v>449.93</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>15</v>
+    <row r="3" spans="1:17" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="C3" s="6">
         <v>2023</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E3" s="6">
         <v>1</v>
@@ -723,16 +804,16 @@
         <v>46.394999999999996</v>
       </c>
       <c r="L3" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="M3" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="N3">
         <v>241.03000000000003</v>
       </c>
       <c r="O3" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="P3">
         <v>35</v>
@@ -741,18 +822,18 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>15</v>
+    <row r="4" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="C4" s="6">
         <v>2023</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E4" s="6">
         <v>1</v>
@@ -776,16 +857,16 @@
         <v>22.520000000000003</v>
       </c>
       <c r="L4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="M4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="N4">
         <v>306.64</v>
       </c>
       <c r="O4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="P4">
         <v>39</v>
@@ -794,18 +875,18 @@
         <v>473.79</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>15</v>
+    <row r="5" spans="1:17" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="C5" s="6">
         <v>2023</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E5" s="6">
         <v>2</v>
@@ -829,16 +910,16 @@
         <v>25.855</v>
       </c>
       <c r="L5" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="M5" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="N5">
         <v>370.94499999999999</v>
       </c>
       <c r="O5" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="P5">
         <v>33.5</v>
@@ -847,18 +928,18 @@
         <v>484.04</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>15</v>
+    <row r="6" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="C6" s="6">
         <v>2023</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
@@ -882,16 +963,16 @@
         <v>23.625</v>
       </c>
       <c r="L6" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="N6">
         <v>344.27499999999998</v>
       </c>
       <c r="O6" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="P6">
         <v>34</v>
@@ -900,18 +981,18 @@
         <v>556.76</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>15</v>
+    <row r="7" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="C7" s="6">
         <v>2023</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E7" s="6">
         <v>2</v>
@@ -935,16 +1016,16 @@
         <v>20.805</v>
       </c>
       <c r="L7" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="M7" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="N7">
         <v>210.61</v>
       </c>
       <c r="O7" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="P7">
         <v>32</v>
@@ -953,18 +1034,18 @@
         <v>497.82</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>15</v>
+    <row r="8" spans="1:17" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="C8" s="6">
         <v>2023</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E8" s="6">
         <v>3</v>
@@ -988,16 +1069,16 @@
         <v>20.92</v>
       </c>
       <c r="L8" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="M8" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="N8">
         <v>243.02500000000001</v>
       </c>
       <c r="O8" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="P8">
         <v>27.5</v>
@@ -1006,18 +1087,18 @@
         <v>495.61</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>15</v>
+    <row r="9" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="C9" s="6">
         <v>2023</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E9" s="6">
         <v>3</v>
@@ -1041,16 +1122,16 @@
         <v>6.07</v>
       </c>
       <c r="L9" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="M9" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="N9">
         <v>348.44499999999999</v>
       </c>
       <c r="O9" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="P9">
         <v>35</v>
@@ -1059,18 +1140,18 @@
         <v>686.07</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>15</v>
+    <row r="10" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="C10" s="6">
         <v>2023</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E10" s="6">
         <v>3</v>
@@ -1094,16 +1175,16 @@
         <v>2.3249999999999997</v>
       </c>
       <c r="L10" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="M10" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="N10">
         <v>338.255</v>
       </c>
       <c r="O10" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="P10">
         <v>32.5</v>
@@ -1112,18 +1193,18 @@
         <v>556.48</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>15</v>
+    <row r="11" spans="1:17" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="C11" s="6">
         <v>2023</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E11" s="6">
         <v>4</v>
@@ -1147,16 +1228,16 @@
         <v>15.885</v>
       </c>
       <c r="L11" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="M11" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="N11">
         <v>261.685</v>
       </c>
       <c r="O11" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="P11">
         <v>40.5</v>
@@ -1165,18 +1246,18 @@
         <v>575.66999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>15</v>
+    <row r="12" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="C12" s="6">
         <v>2023</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E12" s="6">
         <v>4</v>
@@ -1200,16 +1281,16 @@
         <v>11.565</v>
       </c>
       <c r="L12" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="M12" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="N12">
         <v>236.04500000000002</v>
       </c>
       <c r="O12" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="P12">
         <v>34.5</v>
@@ -1218,18 +1299,18 @@
         <v>457.43</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>15</v>
+    <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="C13" s="6">
         <v>2023</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E13" s="6">
         <v>4</v>
@@ -1253,16 +1334,16 @@
         <v>16.835000000000001</v>
       </c>
       <c r="L13" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="M13" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="N13">
         <v>230.035</v>
       </c>
       <c r="O13" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="P13">
         <v>39</v>
@@ -1271,18 +1352,18 @@
         <v>549.80999999999995</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
-        <v>14</v>
+    <row r="14" spans="1:17" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C14" s="6">
         <v>2024</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E14" s="6">
         <v>1</v>
@@ -1318,24 +1399,24 @@
         <v>0.3183919347747895</v>
       </c>
       <c r="P14" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="C15" s="6">
         <v>2024</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E15" s="6">
         <v>1</v>
@@ -1377,18 +1458,18 @@
         <v>660</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
-        <v>19</v>
+    <row r="16" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C16" s="6">
         <v>2024</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E16" s="6">
         <v>1</v>
@@ -1430,18 +1511,18 @@
         <v>624</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
-        <v>21</v>
+    <row r="17" spans="1:17" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C17" s="6">
         <v>2024</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E17" s="6">
         <v>2</v>
@@ -1483,18 +1564,18 @@
         <v>670</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
-        <v>22</v>
+    <row r="18" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C18" s="6">
         <v>2024</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E18" s="6">
         <v>2</v>
@@ -1536,18 +1617,18 @@
         <v>638</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
-        <v>23</v>
+    <row r="19" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C19" s="6">
         <v>2024</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E19" s="6">
         <v>2</v>
@@ -1589,18 +1670,18 @@
         <v>646</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
-        <v>24</v>
+    <row r="20" spans="1:17" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C20" s="6">
         <v>2024</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E20" s="6">
         <v>3</v>
@@ -1642,18 +1723,18 @@
         <v>672</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
-        <v>25</v>
+    <row r="21" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A21" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C21" s="6">
         <v>2024</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E21" s="6">
         <v>3</v>
@@ -1695,18 +1776,18 @@
         <v>604</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
-        <v>26</v>
+    <row r="22" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C22" s="6">
         <v>2024</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E22" s="6">
         <v>3</v>
@@ -1748,18 +1829,18 @@
         <v>586</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
-        <v>27</v>
+    <row r="23" spans="1:17" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C23" s="6">
         <v>2024</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E23" s="6">
         <v>4</v>
@@ -1801,18 +1882,18 @@
         <v>534</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
-        <v>28</v>
+    <row r="24" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C24" s="6">
         <v>2024</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E24" s="6">
         <v>4</v>
@@ -1854,18 +1935,18 @@
         <v>548</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
-        <v>29</v>
+    <row r="25" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C25" s="6">
         <v>2024</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E25" s="6">
         <v>4</v>
@@ -1907,18 +1988,18 @@
         <v>586</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>14</v>
+    <row r="26" spans="1:17" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C26">
         <v>2024</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -1960,18 +2041,18 @@
         <v>638</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>17</v>
+    <row r="27" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A27" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C27">
         <v>2024</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -2013,18 +2094,18 @@
         <v>662</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+    <row r="28" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A28" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" t="s">
         <v>19</v>
-      </c>
-      <c r="B28" t="s">
-        <v>32</v>
       </c>
       <c r="C28">
         <v>2024</v>
       </c>
       <c r="D28" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2066,18 +2147,18 @@
         <v>700</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>21</v>
+    <row r="29" spans="1:17" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C29">
         <v>2024</v>
       </c>
       <c r="D29" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E29">
         <v>2</v>
@@ -2119,18 +2200,18 @@
         <v>626</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>22</v>
+    <row r="30" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A30" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C30">
         <v>2024</v>
       </c>
       <c r="D30" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E30">
         <v>2</v>
@@ -2172,18 +2253,18 @@
         <v>686</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>23</v>
+    <row r="31" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A31" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C31">
         <v>2024</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E31">
         <v>2</v>
@@ -2225,18 +2306,18 @@
         <v>690</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>24</v>
+    <row r="32" spans="1:17" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C32">
         <v>2024</v>
       </c>
       <c r="D32" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E32">
         <v>3</v>
@@ -2278,18 +2359,18 @@
         <v>688</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>25</v>
+    <row r="33" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A33" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C33">
         <v>2024</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E33">
         <v>3</v>
@@ -2331,18 +2412,18 @@
         <v>712</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>26</v>
+    <row r="34" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A34" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C34">
         <v>2024</v>
       </c>
       <c r="D34" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E34">
         <v>3</v>
@@ -2384,18 +2465,18 @@
         <v>666</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>27</v>
+    <row r="35" spans="1:17" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C35">
         <v>2024</v>
       </c>
       <c r="D35" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E35">
         <v>4</v>
@@ -2437,18 +2518,18 @@
         <v>730</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>28</v>
+    <row r="36" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A36" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C36">
         <v>2024</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E36">
         <v>4</v>
@@ -2490,18 +2571,18 @@
         <v>688</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>29</v>
+    <row r="37" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A37" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C37">
         <v>2024</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E37">
         <v>4</v>
@@ -2544,6 +2625,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>